--- a/Acoustics/Exam_1_Folder/low_pass_resistor.xlsx
+++ b/Acoustics/Exam_1_Folder/low_pass_resistor.xlsx
@@ -1,17 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="11_1A0A7A34C5960F447E46777B7253018143AC2DCF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01E90932-D2BA-4128-8AE6-EC868CC04D48}"/>
+  <bookViews>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="13372" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>DataPtNum</t>
   </si>
@@ -27,21 +44,29 @@
   <si>
     <t>phase</t>
   </si>
+  <si>
+    <t>Gain(|Vout/Vin|)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="171" formatCode="0.000"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
@@ -69,9 +94,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -410,15 +436,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E56"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F56"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="11" customWidth="1"/>
     <col min="3" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="20.23046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -434,8 +461,11 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -443,16 +473,20 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>0.952</v>
+        <v>0.95199999999999996</v>
       </c>
       <c r="D2">
-        <v>0.744</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="E2">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" s="2">
+        <f>D2/C2</f>
+        <v>0.78151260504201681</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -460,16 +494,20 @@
         <v>15</v>
       </c>
       <c r="C3">
-        <v>0.952</v>
+        <v>0.95199999999999996</v>
       </c>
       <c r="D3">
-        <v>0.744</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="E3">
         <v>1.78</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" s="2">
+        <f t="shared" ref="F3:F56" si="0">D3/C3</f>
+        <v>0.78151260504201681</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -477,16 +515,20 @@
         <v>20</v>
       </c>
       <c r="C4">
-        <v>0.952</v>
+        <v>0.95199999999999996</v>
       </c>
       <c r="D4">
-        <v>0.744</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="E4">
         <v>1.44</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" s="2">
+        <f t="shared" si="0"/>
+        <v>0.78151260504201681</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>4</v>
       </c>
@@ -497,13 +539,17 @@
         <v>0.96</v>
       </c>
       <c r="D5">
-        <v>0.744</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="E5">
         <v>1.8</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" s="2">
+        <f t="shared" si="0"/>
+        <v>0.77500000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>5</v>
       </c>
@@ -519,8 +565,12 @@
       <c r="E6">
         <v>3.23</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" s="2">
+        <f t="shared" si="0"/>
+        <v>0.79166666666666674</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>6</v>
       </c>
@@ -536,8 +586,12 @@
       <c r="E7">
         <v>3.78</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" s="2">
+        <f t="shared" si="0"/>
+        <v>0.79166666666666674</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>7</v>
       </c>
@@ -553,8 +607,12 @@
       <c r="E8">
         <v>4.32</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" s="2">
+        <f t="shared" si="0"/>
+        <v>0.79166666666666674</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>8</v>
       </c>
@@ -570,8 +628,12 @@
       <c r="E9">
         <v>-1.62</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" s="2">
+        <f t="shared" si="0"/>
+        <v>0.79166666666666674</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>9</v>
       </c>
@@ -587,8 +649,12 @@
       <c r="E10">
         <v>-1.8</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" s="2">
+        <f t="shared" si="0"/>
+        <v>0.79166666666666674</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>10</v>
       </c>
@@ -596,16 +662,20 @@
         <v>55</v>
       </c>
       <c r="C11">
-        <v>0.968</v>
+        <v>0.96799999999999997</v>
       </c>
       <c r="D11">
-        <v>0.768</v>
+        <v>0.76800000000000002</v>
       </c>
       <c r="E11">
         <v>-1.98</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11" s="2">
+        <f t="shared" si="0"/>
+        <v>0.79338842975206614</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>11</v>
       </c>
@@ -613,16 +683,20 @@
         <v>60</v>
       </c>
       <c r="C12">
-        <v>0.9968</v>
+        <v>0.99680000000000002</v>
       </c>
       <c r="D12">
-        <v>0.768</v>
+        <v>0.76800000000000002</v>
       </c>
       <c r="E12">
         <v>-2.17</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12" s="2">
+        <f t="shared" si="0"/>
+        <v>0.7704654895666132</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>12</v>
       </c>
@@ -630,16 +704,20 @@
         <v>65</v>
       </c>
       <c r="C13">
-        <v>0.976</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="D13">
-        <v>0.768</v>
+        <v>0.76800000000000002</v>
       </c>
       <c r="E13">
         <v>-7.01</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13" s="2">
+        <f t="shared" si="0"/>
+        <v>0.78688524590163933</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>13</v>
       </c>
@@ -647,16 +725,20 @@
         <v>70</v>
       </c>
       <c r="C14">
-        <v>0.976</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="D14">
-        <v>0.768</v>
+        <v>0.76800000000000002</v>
       </c>
       <c r="E14">
         <v>-7.5</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14" s="2">
+        <f t="shared" si="0"/>
+        <v>0.78688524590163933</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>14</v>
       </c>
@@ -664,16 +746,20 @@
         <v>75</v>
       </c>
       <c r="C15">
-        <v>0.976</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="D15">
-        <v>0.768</v>
+        <v>0.76800000000000002</v>
       </c>
       <c r="E15">
-        <v>-4.06</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-4.0599999999999996</v>
+      </c>
+      <c r="F15" s="2">
+        <f t="shared" si="0"/>
+        <v>0.78688524590163933</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>15</v>
       </c>
@@ -681,16 +767,20 @@
         <v>80</v>
       </c>
       <c r="C16">
-        <v>0.976</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="D16">
-        <v>0.768</v>
+        <v>0.76800000000000002</v>
       </c>
       <c r="E16">
-        <v>-8.7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-8.6999999999999993</v>
+      </c>
+      <c r="F16" s="2">
+        <f t="shared" si="0"/>
+        <v>0.78688524590163933</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>16</v>
       </c>
@@ -698,16 +788,20 @@
         <v>85</v>
       </c>
       <c r="C17">
-        <v>0.976</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="D17">
-        <v>0.768</v>
+        <v>0.76800000000000002</v>
       </c>
       <c r="E17">
         <v>-3.05</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17" s="2">
+        <f t="shared" si="0"/>
+        <v>0.78688524590163933</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>17</v>
       </c>
@@ -715,16 +809,20 @@
         <v>90</v>
       </c>
       <c r="C18">
-        <v>0.976</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="D18">
-        <v>0.768</v>
+        <v>0.76800000000000002</v>
       </c>
       <c r="E18">
         <v>-3.27</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18" s="2">
+        <f t="shared" si="0"/>
+        <v>0.78688524590163933</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>18</v>
       </c>
@@ -732,16 +830,20 @@
         <v>95</v>
       </c>
       <c r="C19">
-        <v>0.968</v>
+        <v>0.96799999999999997</v>
       </c>
       <c r="D19">
-        <v>0.768</v>
+        <v>0.76800000000000002</v>
       </c>
       <c r="E19">
         <v>-3.4</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19" s="2">
+        <f t="shared" si="0"/>
+        <v>0.79338842975206614</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>19</v>
       </c>
@@ -749,16 +851,20 @@
         <v>100</v>
       </c>
       <c r="C20">
-        <v>0.968</v>
+        <v>0.96799999999999997</v>
       </c>
       <c r="D20">
-        <v>0.768</v>
+        <v>0.76800000000000002</v>
       </c>
       <c r="E20">
         <v>-1.8</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20" s="2">
+        <f t="shared" si="0"/>
+        <v>0.79338842975206614</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>20</v>
       </c>
@@ -766,7 +872,7 @@
         <v>150</v>
       </c>
       <c r="C21">
-        <v>0.968</v>
+        <v>0.96799999999999997</v>
       </c>
       <c r="D21">
         <v>0.76</v>
@@ -774,8 +880,12 @@
       <c r="E21">
         <v>-8.06</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21" s="2">
+        <f t="shared" si="0"/>
+        <v>0.78512396694214881</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>21</v>
       </c>
@@ -783,7 +893,7 @@
         <v>200</v>
       </c>
       <c r="C22">
-        <v>0.976</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="D22">
         <v>0.76</v>
@@ -791,8 +901,12 @@
       <c r="E22">
         <v>-10.8</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22" s="2">
+        <f t="shared" si="0"/>
+        <v>0.77868852459016391</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>22</v>
       </c>
@@ -800,7 +914,7 @@
         <v>250</v>
       </c>
       <c r="C23">
-        <v>0.984</v>
+        <v>0.98399999999999999</v>
       </c>
       <c r="D23">
         <v>0.76</v>
@@ -808,8 +922,12 @@
       <c r="E23">
         <v>-11.7</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23" s="2">
+        <f t="shared" si="0"/>
+        <v>0.77235772357723576</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>23</v>
       </c>
@@ -817,16 +935,20 @@
         <v>300</v>
       </c>
       <c r="C24">
-        <v>0.992</v>
+        <v>0.99199999999999999</v>
       </c>
       <c r="D24">
-        <v>0.776</v>
+        <v>0.77600000000000002</v>
       </c>
       <c r="E24">
         <v>-10.8</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24" s="2">
+        <f t="shared" si="0"/>
+        <v>0.78225806451612911</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>24</v>
       </c>
@@ -834,16 +956,20 @@
         <v>350</v>
       </c>
       <c r="C25">
-        <v>0.992</v>
+        <v>0.99199999999999999</v>
       </c>
       <c r="D25">
-        <v>0.768</v>
+        <v>0.76800000000000002</v>
       </c>
       <c r="E25">
-        <v>-16.4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-16.399999999999999</v>
+      </c>
+      <c r="F25" s="2">
+        <f t="shared" si="0"/>
+        <v>0.77419354838709675</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>25</v>
       </c>
@@ -851,16 +977,20 @@
         <v>400</v>
       </c>
       <c r="C26">
-        <v>0.992</v>
+        <v>0.99199999999999999</v>
       </c>
       <c r="D26">
-        <v>0.768</v>
+        <v>0.76800000000000002</v>
       </c>
       <c r="E26">
         <v>-18.7</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F26" s="2">
+        <f t="shared" si="0"/>
+        <v>0.77419354838709675</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>26</v>
       </c>
@@ -876,8 +1006,12 @@
       <c r="E27">
         <v>-21.1</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F27" s="2">
+        <f t="shared" si="0"/>
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>27</v>
       </c>
@@ -893,8 +1027,12 @@
       <c r="E28">
         <v>-19.8</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F28" s="2">
+        <f t="shared" si="0"/>
+        <v>0.75247524752475248</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>28</v>
       </c>
@@ -910,8 +1048,12 @@
       <c r="E29">
         <v>-29.7</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F29" s="2">
+        <f t="shared" si="0"/>
+        <v>0.75247524752475248</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>29</v>
       </c>
@@ -927,8 +1069,12 @@
       <c r="E30">
         <v>-30</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F30" s="2">
+        <f t="shared" si="0"/>
+        <v>0.74509803921568629</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>30</v>
       </c>
@@ -942,10 +1088,14 @@
         <v>0.76</v>
       </c>
       <c r="E31">
-        <v>-33.2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-33.200000000000003</v>
+      </c>
+      <c r="F31" s="2">
+        <f t="shared" si="0"/>
+        <v>0.74509803921568629</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>31</v>
       </c>
@@ -961,8 +1111,12 @@
       <c r="E32">
         <v>-25.7</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F32" s="2">
+        <f t="shared" si="0"/>
+        <v>0.73786407766990292</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>32</v>
       </c>
@@ -978,8 +1132,12 @@
       <c r="E33">
         <v>-37.1</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F33" s="2">
+        <f t="shared" si="0"/>
+        <v>0.72307692307692306</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>33</v>
       </c>
@@ -995,8 +1153,12 @@
       <c r="E34">
         <v>-39.4</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F34" s="2">
+        <f t="shared" si="0"/>
+        <v>0.71619047619047616</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1012,8 +1174,12 @@
       <c r="E35">
         <v>-42</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F35" s="2">
+        <f t="shared" si="0"/>
+        <v>0.71619047619047616</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1029,8 +1195,12 @@
       <c r="E36">
         <v>-41.8</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F36" s="2">
+        <f t="shared" si="0"/>
+        <v>0.7094339622641509</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1041,13 +1211,17 @@
         <v>1.08</v>
       </c>
       <c r="D37">
-        <v>0.744</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="E37">
         <v>-51.9</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F37" s="2">
+        <f t="shared" si="0"/>
+        <v>0.68888888888888888</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1055,16 +1229,20 @@
         <v>1000</v>
       </c>
       <c r="C38">
-        <v>1.09</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="D38">
-        <v>0.744</v>
+        <v>0.74399999999999999</v>
       </c>
       <c r="E38">
         <v>-50.4</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F38" s="2">
+        <f t="shared" si="0"/>
+        <v>0.68256880733944947</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1080,8 +1258,12 @@
       <c r="E39">
         <v>-47.7</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F39" s="2">
+        <f t="shared" si="0"/>
+        <v>0.58064516129032251</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1092,13 +1274,17 @@
         <v>1.48</v>
       </c>
       <c r="D40">
-        <v>0.696</v>
+        <v>0.69599999999999995</v>
       </c>
       <c r="E40">
         <v>-82.1</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F40" s="2">
+        <f t="shared" si="0"/>
+        <v>0.47027027027027024</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1109,13 +1295,17 @@
         <v>1.74</v>
       </c>
       <c r="D41">
-        <v>0.656</v>
+        <v>0.65600000000000003</v>
       </c>
       <c r="E41">
         <v>-90</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F41" s="2">
+        <f t="shared" si="0"/>
+        <v>0.37701149425287356</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1126,13 +1316,17 @@
         <v>2.02</v>
       </c>
       <c r="D42">
-        <v>0.616</v>
+        <v>0.61599999999999999</v>
       </c>
       <c r="E42">
         <v>-110.6</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F42" s="2">
+        <f t="shared" si="0"/>
+        <v>0.30495049504950494</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1143,13 +1337,17 @@
         <v>2.34</v>
       </c>
       <c r="D43">
-        <v>0.584</v>
+        <v>0.58399999999999996</v>
       </c>
       <c r="E43">
         <v>-114.1</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F43" s="2">
+        <f t="shared" si="0"/>
+        <v>0.24957264957264957</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1160,13 +1358,17 @@
         <v>2.66</v>
       </c>
       <c r="D44">
-        <v>0.552</v>
+        <v>0.55200000000000005</v>
       </c>
       <c r="E44">
         <v>-124.8</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F44" s="2">
+        <f t="shared" si="0"/>
+        <v>0.20751879699248121</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1177,13 +1379,17 @@
         <v>3</v>
       </c>
       <c r="D45">
-        <v>0.512</v>
+        <v>0.51200000000000001</v>
       </c>
       <c r="E45">
         <v>-121.1</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F45" s="2">
+        <f t="shared" si="0"/>
+        <v>0.17066666666666666</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1197,10 +1403,14 @@
         <v>0.48</v>
       </c>
       <c r="E46">
-        <v>-133.2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-133.19999999999999</v>
+      </c>
+      <c r="F46" s="2">
+        <f t="shared" si="0"/>
+        <v>0.14285714285714285</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1216,8 +1426,12 @@
       <c r="E47">
         <v>-132</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F47" s="2">
+        <f t="shared" si="0"/>
+        <v>0.12228260869565218</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1228,13 +1442,17 @@
         <v>4</v>
       </c>
       <c r="D48">
-        <v>0.424</v>
+        <v>0.42399999999999999</v>
       </c>
       <c r="E48">
         <v>-141</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F48" s="2">
+        <f t="shared" si="0"/>
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1248,10 +1466,14 @@
         <v>0.376</v>
       </c>
       <c r="E49">
-        <v>-133.2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-133.19999999999999</v>
+      </c>
+      <c r="F49" s="2">
+        <f t="shared" si="0"/>
+        <v>8.7850467289719625E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1259,7 +1481,7 @@
         <v>7000</v>
       </c>
       <c r="C50">
-        <v>4.56</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="D50">
         <v>0.36</v>
@@ -1267,8 +1489,12 @@
       <c r="E50">
         <v>-142.5</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F50" s="2">
+        <f t="shared" si="0"/>
+        <v>7.8947368421052641E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1279,13 +1505,17 @@
         <v>4.84</v>
       </c>
       <c r="D51">
-        <v>0.328</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="E51">
         <v>-137</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F51" s="2">
+        <f t="shared" si="0"/>
+        <v>6.7768595041322321E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1299,10 +1529,14 @@
         <v>0.312</v>
       </c>
       <c r="E52">
-        <v>-145.7</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-145.69999999999999</v>
+      </c>
+      <c r="F52" s="2">
+        <f t="shared" si="0"/>
+        <v>6.1417322834645668E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1313,13 +1547,17 @@
         <v>5.32</v>
       </c>
       <c r="D53">
-        <v>0.296</v>
+        <v>0.29599999999999999</v>
       </c>
       <c r="E53">
         <v>-143.4</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F53" s="2">
+        <f t="shared" si="0"/>
+        <v>5.5639097744360898E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1330,13 +1568,17 @@
         <v>5.56</v>
       </c>
       <c r="D54">
-        <v>0.28</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="E54">
         <v>-151.1</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F54" s="2">
+        <f t="shared" si="0"/>
+        <v>5.0359712230215833E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1347,13 +1589,17 @@
         <v>5.8</v>
       </c>
       <c r="D55">
-        <v>0.264</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="E55">
-        <v>-139.2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+        <v>-139.19999999999999</v>
+      </c>
+      <c r="F55" s="2">
+        <f t="shared" si="0"/>
+        <v>4.5517241379310347E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1367,11 +1613,15 @@
         <v>0.248</v>
       </c>
       <c r="E56">
-        <v>-154.8</v>
+        <v>-154.80000000000001</v>
+      </c>
+      <c r="F56" s="2">
+        <f t="shared" si="0"/>
+        <v>4.1333333333333333E-2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>